--- a/education_enrollment_forms/011_multicultural_classroom_development_registration_form--education_enrollment_forms.xlsx
+++ b/education_enrollment_forms/011_multicultural_classroom_development_registration_form--education_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'bachelor',_'value':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Bachelor', 'value': 'bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'master',_'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Master', 'value': 'master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'doctoral',_'value':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Doctoral', 'value': 'doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'diversity',_'value':_'diversity'}</t>
+          <t>diversity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Diversity', 'value': 'diversity'}</t>
+          <t>Diversity</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'classroom_management',_'value':_'classroom_management'}</t>
+          <t>classroom_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Classroom Management', 'value': 'classroom_management'}</t>
+          <t>Classroom Management</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'leadership',_'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership', 'value': 'leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person', 'value': 'in-person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_confirm_that_my_submission_is_complete_and_accurate.',_'value':_'i_confirm_that_my_submission_is_complete_and_accurate.'}</t>
+          <t>i_confirm_that_my_submission_is_complete_and_accurate.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I confirm that my submission is complete and accurate.', 'value': 'I confirm that my submission is complete and accurate.'}</t>
+          <t>I confirm that my submission is complete and accurate.</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_yet',_'value':_'not_yet'}</t>
+          <t>not_yet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not yet', 'value': 'not_yet'}</t>
+          <t>Not yet</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
